--- a/src/assets/MCL-Warehouse_Location.xlsx
+++ b/src/assets/MCL-Warehouse_Location.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mclwebsite\src\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E23E0C-7162-4840-BA75-DABC80FFBA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A51DE1-D02E-4461-8475-8869EE03C64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse Locations" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>MCL Warehouses Google Locations</t>
   </si>
@@ -104,13 +104,49 @@
   </si>
   <si>
     <t>33.995168150031574, 71.61108638650464</t>
+  </si>
+  <si>
+    <t>Arifwala Warehouse</t>
+  </si>
+  <si>
+    <t>Bahawalpur Warehouse</t>
+  </si>
+  <si>
+    <t>Karachi Warehouse</t>
+  </si>
+  <si>
+    <t>Therparker Warehouse</t>
+  </si>
+  <si>
+    <t>PGS SHOP MULTAN</t>
+  </si>
+  <si>
+    <t>MULTAN HEAD OFFICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30°14'52.8"N 73°03'49.9"E </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29°25'18.3"N 71°38'54.3"E </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24°51'59.8"N 66°56'12.3"E </t>
+  </si>
+  <si>
+    <t>24°41'54.5"N 70°14'58.1"E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30°11'21.5"N 71°27'54.7"E </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30°08'30.4"N 71°23'41.8"E </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,8 +176,23 @@
       <color rgb="FF0563C1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0563C1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -168,8 +219,14 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -192,11 +249,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF4472C4"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF4472C4"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF4472C4"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF4472C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -223,6 +295,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -558,7 +642,7 @@
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="13" t="s">
         <v>5</v>
       </c>
     </row>
@@ -672,15 +756,81 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="12" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="11">
+        <v>13</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="11">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="11">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="11">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="11">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -688,19 +838,20 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="C6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C7" r:id="rId5" display="https://maps.app.goo.gl/awkCn169zBoRxXCJ6" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="C8" r:id="rId6" display="https://maps.app.goo.gl/wP5WPknaLc4SZQAdA" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="C9" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="C10" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="C11" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="C12" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="C13" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="C14" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="C9" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="C10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="C11" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="C12" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="C13" r:id="rId5" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="C14" r:id="rId6" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="C8" r:id="rId7" display="https://maps.app.goo.gl/wP5WPknaLc4SZQAdA" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C7" r:id="rId8" display="https://maps.app.goo.gl/awkCn169zBoRxXCJ6" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C6" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C5" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C4" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C3" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>